--- a/event_registration_forms/024_event_seating_arrangement_form--event_registration_forms.xlsx
+++ b/event_registration_forms/024_event_seating_arrangement_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'festival'}</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'festival'}</t>
+          <t>festival</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'round_table'}</t>
+          <t>round_table</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'round_table'}</t>
+          <t>round table</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'rectangular_table'}</t>
+          <t>rectangular_table</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'rectangular_table'}</t>
+          <t>rectangular table</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'buffet'}</t>
+          <t>buffet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'buffet'}</t>
+          <t>buffet</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'small'}</t>
+          <t>small</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'large'}</t>
+          <t>large</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'extra_large'}</t>
+          <t>extra large</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'linear'}</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'linear'}</t>
+          <t>linear</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'u_shaped'}</t>
+          <t>u_shaped</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'u_shaped'}</t>
+          <t>u shaped</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'horseshoe'}</t>
+          <t>horseshoe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'horseshoe'}</t>
+          <t>horseshoe</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'white'}</t>
+          <t>white</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'black'}</t>
+          <t>black</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'vip'}</t>
+          <t>vip</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'vip'}</t>
+          <t>vip</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'wheelchair_accessible'}</t>
+          <t>wheelchair_accessible</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'wheelchair_accessible'}</t>
+          <t>wheelchair accessible</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'plain'}</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'plain'}</t>
+          <t>plain</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'lace'}</t>
+          <t>lace</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'lace'}</t>
+          <t>lace</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'flowers'}</t>
+          <t>flowers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'flowers'}</t>
+          <t>flowers</t>
         </is>
       </c>
     </row>
